--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R2" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R3" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R4" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R5" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>97789</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R6" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1187,9 @@
           <t>2001-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1308,12 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>96820</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R7" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1378,19 +1298,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1434,12 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R8" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1504,19 +1409,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1560,12 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R9" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1630,19 +1520,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1686,12 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R10" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1756,19 +1631,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1812,12 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R11" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1882,19 +1742,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1938,12 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R12" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2008,19 +1853,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2064,12 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R13" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2134,19 +1964,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2190,12 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>100908</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103280</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R14" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2260,19 +2075,9 @@
           <t>2001-01-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2316,12 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444118.599771456</v>
+        <v>444119</v>
       </c>
       <c r="R15" t="n">
-        <v>6392372.753102533</v>
+        <v>6392373</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2386,19 +2186,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100086</v>
+        <v>100092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99108</v>
+        <v>99113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100790</v>
+        <v>100796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103280</v>
+        <v>103288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100092</v>
+        <v>100093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99113</v>
+        <v>99114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100796</v>
+        <v>100797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103288</v>
+        <v>103290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99248</v>
+        <v>99275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100093</v>
+        <v>100120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99114</v>
+        <v>99141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100797</v>
+        <v>100824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103290</v>
+        <v>103317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100120</v>
+        <v>100126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99141</v>
+        <v>99147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100824</v>
+        <v>100830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103317</v>
+        <v>103323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99281</v>
+        <v>99288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100126</v>
+        <v>100133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99147</v>
+        <v>99154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100830</v>
+        <v>100837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103323</v>
+        <v>103330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100133</v>
+        <v>100137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99154</v>
+        <v>99158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100837</v>
+        <v>100841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103330</v>
+        <v>103334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99292</v>
+        <v>99299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100137</v>
+        <v>100144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99158</v>
+        <v>99165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100841</v>
+        <v>100848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103334</v>
+        <v>103341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100147</v>
+        <v>100152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99168</v>
+        <v>99173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100851</v>
+        <v>100856</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103344</v>
+        <v>103349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101914</v>
+        <v>101919</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99307</v>
+        <v>99315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100152</v>
+        <v>100160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99173</v>
+        <v>99181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100856</v>
+        <v>100864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103349</v>
+        <v>103357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101919</v>
+        <v>101927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982903</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208911</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74247146</v>
       </c>
       <c r="B4" t="n">
-        <v>99315</v>
+        <v>99325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74411812</v>
       </c>
       <c r="B5" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74462191</v>
       </c>
       <c r="B6" t="n">
-        <v>100160</v>
+        <v>100170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74531935</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74561014</v>
       </c>
       <c r="B8" t="n">
-        <v>101736</v>
+        <v>101746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74553469</v>
       </c>
       <c r="B9" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74604535</v>
       </c>
       <c r="B10" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74767520</v>
       </c>
       <c r="B11" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>74858747</v>
       </c>
       <c r="B12" t="n">
-        <v>100864</v>
+        <v>100874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>74965179</v>
       </c>
       <c r="B13" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>74943170</v>
       </c>
       <c r="B14" t="n">
-        <v>103357</v>
+        <v>103367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>75151564</v>
       </c>
       <c r="B15" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982903</v>
+        <v>74858745</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>101344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
+          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Hypochoeris maculata. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Pulsatilla vernalis. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grusvägkanter, ängsmark, betesmark</t>
+          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,38 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74208911</v>
+        <v>74943170</v>
       </c>
       <c r="B3" t="n">
-        <v>99298</v>
+        <v>103857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222295</v>
+        <v>1932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Källblekvide</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Salix hastata subsp. vegeta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(Andersson) Flod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m S Kåperyd, Sm</t>
+          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Carex caryophyllea. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Salix hastata ssp. vegeta. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kulturmark, vägrenar, hällar, åkerkanter, gård</t>
+          <t>Fuktäng, åkanter, kärr</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,38 +897,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74247146</v>
+        <v>74553469</v>
       </c>
       <c r="B4" t="n">
-        <v>99325</v>
+        <v>107608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222309</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
+          <t>Kåperyd. 300m S Kåperyd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -962,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Carex ericetorum. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lathraea squamaria. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grusvägkanter, ängsmark, betesmark</t>
+          <t>Kulturmark, vägrenar, hällar, åkerkanter, gård</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,38 +1008,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74411812</v>
+        <v>74767520</v>
       </c>
       <c r="B5" t="n">
-        <v>106294</v>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
+          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Fraxinus excelsior. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Platanthera chlorantha. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grusvägkanter, ängsmark, betesmark</t>
+          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,38 +1119,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74462191</v>
+        <v>73982902</v>
       </c>
       <c r="B6" t="n">
-        <v>100170</v>
+        <v>109814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221660</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrönt mannagräs</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glyceria declinata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bréb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
+          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2001-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Glyceria declinata. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Hypochoeris maculata. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Fuktäng, åkanter, kärr</t>
+          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74531935</v>
+        <v>74965179</v>
       </c>
       <c r="B7" t="n">
-        <v>99191</v>
+        <v>110077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222541</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Juncus squarrosus. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Scorzonera humilis. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,38 +1341,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74561014</v>
+        <v>74411811</v>
       </c>
       <c r="B8" t="n">
-        <v>101746</v>
+        <v>106812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
+          <t>Kåperyd. 300m S Kåperyd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lathyrus niger. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Fraxinus excelsior. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grusvägkanter, ängsmark, betesmark</t>
+          <t>Kulturmark, vägrenar, hällar, åkerkanter, gård</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,38 +1452,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74553469</v>
+        <v>74561014</v>
       </c>
       <c r="B9" t="n">
-        <v>107084</v>
+        <v>102224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219686</v>
+        <v>221223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m S Kåperyd, Sm</t>
+          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>1984-12-31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lathraea squamaria. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lathyrus niger. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kulturmark, vägrenar, hällar, åkerkanter, gård</t>
+          <t>Grusvägkanter, ängsmark, betesmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,38 +1563,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74604535</v>
+        <v>75151564</v>
       </c>
       <c r="B10" t="n">
-        <v>97543</v>
+        <v>102418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>221317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåperyd. 300m S Kåperyd, Sm</t>
+          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lycopodium clavatum. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Trifolium aureum. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kulturmark, vägrenar, hällar, åkerkanter, gård</t>
+          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1674,38 +1674,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74767520</v>
+        <v>74462191</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>100631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219875</v>
+        <v>221660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blågrönt mannagräs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Glyceria declinata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Bréb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
+          <t>Kåperyd. 300m SV Kåperyd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Platanthera chlorantha. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Glyceria declinata. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
+          <t>Fuktäng, åkanter, kärr</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,32 +1785,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74858747</v>
+        <v>74604534</v>
       </c>
       <c r="B12" t="n">
-        <v>100874</v>
+        <v>97986</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1853</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Pulsatilla vernalis. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Lycopodium clavatum. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>74965179</v>
+        <v>74208908</v>
       </c>
       <c r="B13" t="n">
-        <v>109528</v>
+        <v>99754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Scorzonera humilis. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Carex caryophyllea. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,32 +2007,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>74943170</v>
+        <v>74247146</v>
       </c>
       <c r="B14" t="n">
-        <v>103367</v>
+        <v>99781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1932</v>
+        <v>222309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Källblekvide</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Salix hastata subsp. vegeta</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Andersson) Flod.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,17 +2072,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2001-12-31</t>
+          <t>1984-12-31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Salix hastata ssp. vegeta. LEG: Hans Thulin</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Carex ericetorum. LEG: Hans Thulin</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Fuktäng, åkanter, kärr</t>
+          <t>Grusvägkanter, ängsmark, betesmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>75151564</v>
+        <v>5114394</v>
       </c>
       <c r="B15" t="n">
-        <v>101937</v>
+        <v>99646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,37 +2129,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221317</v>
+        <v>222541</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
+          <t>Kåperyd,Kärrån, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444119</v>
+        <v>444179</v>
       </c>
       <c r="R15" t="n">
-        <v>6392373</v>
+        <v>6392304</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,17 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2002-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Trifolium aureum. LEG: Hans Thulin</t>
+          <t>2002-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,25 +2202,245 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
+          <t>Fuktig stigkant</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74531935</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99646</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222541</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Borsttåg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kåperyd. 200m SSV Kåperyds gård, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>444119</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6392373</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D9j 0210. SOM: Juncus squarrosus. LEG: Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Betad sydsluttning, ängshage, bäckkanter, myr, kärr</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5264392</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kärrån,Kåperyd,Taberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>444200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6392294</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2002-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2002-08-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35568-2025 artfynd.xlsx
+++ b/artfynd/A 35568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74858745</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74943170</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74553469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74767520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74965179</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74411811</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74561014</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75151564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74462191</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74604534</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74208908</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74247146</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,6 +2287,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5114394</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2328,6 +2403,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74531935</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2441,8 +2521,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5264392</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>